--- a/tests/fixtures/sample_template.xlsx
+++ b/tests/fixtures/sample_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:D7"/>
+  <dimension ref="B3:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
@@ -437,6 +437,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{{客户名}}和{{编号}}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/fixtures/sample_template.xlsx
+++ b/tests/fixtures/sample_template.xlsx
@@ -413,34 +413,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:E9"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="3">
-      <c r="B3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>{{编号}}</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{{姓名}}</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{{部门}}</t>
+        </is>
+      </c>
     </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{{姓名}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>normal_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>{{客户名}}和{{编号}}</t>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>报告日期：{{日期}}</t>
         </is>
       </c>
     </row>
